--- a/results/log_pv_cap_fit/log_pv_cap_fit_densities_adensity_estimates.xlsx
+++ b/results/log_pv_cap_fit/log_pv_cap_fit_densities_adensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>adensity</t>
+          <t>D(Firm assets)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.000*</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.324***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-1.155***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-1.155***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-1.155***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2.155***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.155***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.155***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.002*</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.150***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.293+</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.293+</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.293+</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.236***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.236***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.236***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_adensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.897***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.000*</t>
+          <t>0.745***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.000*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.618***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.958***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.809***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.706***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.384**</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.588***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.835***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.977***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.909***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.852***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Firm assets))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.051**</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.007+</t>
+          <t>-0.000*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>-0.000*</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.222***</t>
+          <t>0.384**</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.279***</t>
+          <t>0.588***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.312***</t>
+          <t>0.835***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.897***</t>
+          <t>-0.051**</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.745***</t>
+          <t>-0.007+</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.618***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.958***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.809***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.706***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>-0.222***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>-0.279***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.843</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.879</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.860</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.838</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.233</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.441</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.501</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
+          <t>-0.312***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-9989.123</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9543.957</t>
+          <t>0.862</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9265.371</t>
+          <t>0.843</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-9970.932</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9470.696</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9126.701</t>
+          <t>0.838</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9973.453</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9363.140</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8907.486</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1533.394</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1533.394</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1533.394</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2871.682</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2871.682</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2871.682</t>
+          <t>0.501</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9938.379</t>
+          <t>-9989.123</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9493.213</t>
+          <t>-9543.957</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9214.627</t>
+          <t>-9265.371</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9942.741</t>
+          <t>-9970.932</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9442.505</t>
+          <t>-9470.696</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9098.510</t>
+          <t>-9126.701</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9950.901</t>
+          <t>-9973.453</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9340.587</t>
+          <t>-9363.140</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8884.933</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1561.585</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1561.585</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1561.585</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2899.873</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2899.873</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2899.873</t>
+          <t>-8907.486</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5003.561</t>
+          <t>-9938.379</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4780.979</t>
+          <t>-9493.213</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4641.685</t>
+          <t>-9214.627</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4990.466</t>
+          <t>-9942.741</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4740.348</t>
+          <t>-9442.505</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4568.350</t>
+          <t>-9098.510</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4990.727</t>
+          <t>-9950.901</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4685.570</t>
+          <t>-9340.587</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4457.743</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-761.697</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-761.697</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-761.697</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1430.841</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1430.841</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1430.841</t>
+          <t>-8884.933</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5003.561</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4780.979</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4641.685</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4990.466</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4740.348</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4568.350</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4990.727</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4685.570</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4457.743</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.973882   1      0.0
-1  LM Marginal Spatial (LM2)    19.444267   1      0.0
-2             LM Joint (LMJ)  4863.580397   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.973882   1      0.0
-1  LM Marginal Spatial (LM2)     8.394312   1      0.0
-2             LM Joint (LMJ)  4555.965370   2      0.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.973882   1      0.0
-1  LM Marginal Spatial (LM2)     8.778984   1      0.0
-2             LM Joint (LMJ)  4562.571455   2      0.0</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  170.368147  1     0.0
-1  Hausman Specification Test -141.514982  4     1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial    42.06902  1     0.0
-1  Hausman Specification Test -141.514982  4     1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   28.574322  1     0.0
-1  Hausman Specification Test -141.514982  4     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000005  0.000002   2.515655  0.011881
-1         log_income     0.061953   0.07008   0.884029  0.376681
-2         log_hholds     0.000582  0.001139   0.510848  0.609457
-3    log_sunny_hours     0.106774  0.032898   3.245636  0.001172
-4         W_adensity     -0.00005  0.000053  -0.927413  0.353712
-5       W_log_income     0.383986  0.131388   2.922539  0.003472
-6       W_log_hholds    -0.050505  0.017506  -2.885043  0.003914
-7  W_log_sunny_hours    -0.221993  0.052539  -4.225301  0.000024
-8   W_log_pv_cap_fit     0.896979  0.025387  35.332567       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000004  0.000002   1.997107  0.045814
-1         log_income     0.105817   0.07184   1.472942  0.140767
-2         log_hholds     0.000851  0.001222   0.696219  0.486291
-3    log_sunny_hours     0.096674  0.033468   2.888544   0.00387
-4         W_adensity    -0.000015  0.000007    -2.1829  0.029043
-5       W_log_income     0.587793  0.089165   6.592189       0.0
-6       W_log_hholds    -0.006834   0.00361  -1.892964  0.058363
-7  W_log_sunny_hours    -0.278595  0.044297   -6.28927       0.0
-8   W_log_pv_cap_fit     0.745388  0.018837  39.569973       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000004  0.000002   1.687666  0.091475
-1         log_income     0.156161  0.073217   2.132835  0.032938
-2         log_hholds     0.000705  0.001299   0.543006  0.587126
-3    log_sunny_hours     0.077099  0.034861   2.211639  0.026992
-4         W_adensity    -0.000008  0.000004    -2.1728  0.029795
-5       W_log_income      0.83516  0.085621   9.754107       0.0
-6       W_log_hholds    -0.007967  0.002129  -3.742186  0.000182
-7  W_log_sunny_hours    -0.311597  0.043653  -7.138048       0.0
-8   W_log_pv_cap_fit     0.618277  0.020628  29.972482       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          adensity     0.000005  0.000002   2.456107  0.014045
-1        log_income     0.080212  0.030404   2.638172  0.008335
-2        log_hholds     0.000692  0.001138    0.60781  0.543314
-3   log_sunny_hours     0.033004  0.022919   1.440018  0.149862
-4  W_log_pv_cap_fit     0.958079  0.010952  87.476724       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          adensity     0.000004  0.000002   1.930185  0.053584
-1        log_income     0.423998  0.037137  11.416999       0.0
-2        log_hholds     0.001254  0.001228   1.021217  0.307152
-3   log_sunny_hours    -0.009224  0.024027  -0.383914  0.701043
-4  W_log_pv_cap_fit     0.809272  0.014253  56.778916       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          adensity     0.000004  0.000002   1.680918  0.092779
-1        log_income     0.644856  0.041994  15.355788       0.0
-2        log_hholds     0.001209  0.001321   0.915147  0.360115
-3   log_sunny_hours     -0.03009  0.025835  -1.164675  0.244151
-4  W_log_pv_cap_fit     0.706425  0.016414  43.036791       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         adensity     0.000005  0.000002    2.560702  0.010446
-1       log_income     0.077566  0.069936    1.109094   0.26739
-2       log_hholds     0.000893  0.001134    0.787198  0.431166
-3  log_sunny_hours     0.107168   0.03294    3.253446   0.00114
-4           lambda     0.977216  0.006357  153.713887       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         adensity     0.000005  0.000002    2.523897  0.011606
-1       log_income      0.21682  0.069672    3.112022  0.001858
-2       log_hholds     0.001794  0.001161    1.545757  0.122163
-3  log_sunny_hours     0.132291  0.033629    3.933855  0.000084
-4           lambda     0.909433  0.008661  105.002744       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         adensity     0.000005  0.000002  2.221777  0.026298
-1       log_income     0.324495  0.070775  4.584872  0.000005
-2       log_hholds     0.002365   0.00117  2.020739  0.043307
-3  log_sunny_hours     0.150181  0.035601  4.218479  0.000025
-4           lambda     0.851899  0.011747  72.52019       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.685583  0.532833  14.423998       0.0
-1         adensity     -0.00004  0.000029   -1.36999  0.170839
-2       log_income    -1.155263  0.079605 -14.512465       0.0
-3       log_hholds     0.002321  0.009276   0.250214  0.802446
-4  log_sunny_hours     0.292991  0.167388   1.750376  0.080202</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.685583  0.532833  14.423998       0.0
-1         adensity     -0.00004  0.000029   -1.36999  0.170839
-2       log_income    -1.155263  0.079605 -14.512465       0.0
-3       log_hholds     0.002321  0.009276   0.250214  0.802446
-4  log_sunny_hours     0.292991  0.167388   1.750376  0.080202</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.685583  0.532833  14.423998       0.0
-1         adensity     -0.00004  0.000029   -1.36999  0.170839
-2       log_income    -1.155263  0.079605 -14.512465       0.0
-3       log_hholds     0.002321  0.009276   0.250214  0.802446
-4  log_sunny_hours     0.292991  0.167388   1.750376  0.080202</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.798454  0.207965 -23.073399       0.0
-1         adensity     0.000002  0.000004   0.620484  0.534939
-2       log_income     2.155248  0.043471  49.579224       0.0
-3       log_hholds     -0.00014  0.002266  -0.061665   0.95083
-4  log_sunny_hours    -0.235719  0.044306  -5.320261       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.798454  0.207965 -23.073399       0.0
-1         adensity     0.000002  0.000004   0.620484  0.534939
-2       log_income     2.155248  0.043471  49.579224       0.0
-3       log_hholds     -0.00014  0.002266  -0.061665   0.95083
-4  log_sunny_hours    -0.235719  0.044306  -5.320261       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.798454  0.207965 -23.073399       0.0
-1         adensity     0.000002  0.000004   0.620484  0.534939
-2       log_income     2.155248  0.043471  49.579224       0.0
-3       log_hholds     -0.00014  0.002266  -0.061665   0.95083
-4  log_sunny_hours    -0.235719  0.044306  -5.320261       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-adensity                                    -0.000433   
-log_income                                   4.328604   
-log_hholds                                  -0.484588   
-log_sunny_hours                             -1.118397   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-adensity                                      0.000005   
-log_income                                    0.061953   
-log_hholds                                    0.000582   
-log_sunny_hours                               0.106774   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-adensity                                       -0.000438  
-log_income                                      4.266651  
-log_hholds                                     -0.485170  
-log_sunny_hours                                -1.225171  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-adensity                             -0.000040   
-log_income                            2.724178   
-log_hholds                           -0.023500   
-log_sunny_hours                      -0.714502   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-adensity                               0.000004   
-log_income                             0.105817   
-log_hholds                             0.000851   
-log_sunny_hours                        0.096674   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-adensity                                -0.000045  
-log_income                               2.618361  
-log_hholds                              -0.024351  
-log_sunny_hours                         -0.811176  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-adensity                         -0.000012                    0.000004   
-log_income                        2.596964                    0.156161   
-log_hholds                       -0.019023                    0.000705   
-log_sunny_hours                  -0.614315                    0.077099   
-                 indirect_ML_LagFE(SLX)_queen  
-adensity                            -0.000016  
-log_income                           2.440803  
-log_hholds                          -0.019729  
-log_sunny_hours                     -0.691413  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-adensity                                0.000116   
-log_income                              1.913384   
-log_hholds                              0.016497   
-log_sunny_hours                         0.787290   
-                 direct_ML_LagFE_inverse_distance  \
-adensity                                 0.000005   
-log_income                               0.080212   
-log_hholds                               0.000692   
-log_sunny_hours                          0.033004   
-                 indirect_ML_LagFE_inverse_distance  
-adensity                                   0.000111  
-log_income                                 1.833172  
-log_hholds                                 0.015806  
-log_sunny_hours                            0.754285  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-adensity                         0.000022                   0.000004   
-log_income                       2.223050                   0.423998   
-log_hholds                       0.006573                   0.001254   
-log_sunny_hours                 -0.048363                  -0.009224   
-                 indirect_ML_LagFE_k_nearest  
-adensity                            0.000018  
-log_income                          1.799052  
-log_hholds                          0.005319  
-log_sunny_hours                    -0.039138  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-adensity                     0.000013               0.000004   
-log_income                   2.196562               0.644856   
-log_hholds                   0.004117               0.001209   
-log_sunny_hours             -0.102495              -0.030090   
-                 indirect_ML_LagFE_queen  
-adensity                        0.000009  
-log_income                      1.551706  
-log_hholds                      0.002909  
-log_sunny_hours                -0.072405  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.977***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.909***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.852***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>7.686***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>7.686***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>7.686***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.798***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.798***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.798***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
